--- a/bancotbj/bancotbj.xlsx
+++ b/bancotbj/bancotbj.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,18 +459,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>corrente</t>
+          <t>CORRENTE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>443</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>400</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cleiton</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>POUPANCA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>401</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
